--- a/artfynd/A 635-2022 artfynd.xlsx
+++ b/artfynd/A 635-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 635-2022 artfynd.xlsx
+++ b/artfynd/A 635-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112090026</v>
+        <v>112090027</v>
       </c>
       <c r="B2" t="n">
-        <v>90893</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574000</v>
+        <v>574002</v>
       </c>
       <c r="R2" t="n">
-        <v>6347541</v>
+        <v>6347542</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112090027</v>
+        <v>110423640</v>
       </c>
       <c r="B3" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>222133</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Utmed riksväg 37/47 Bockara-Århult, Sm</t>
+          <t>Utmed riksväg 37/47 söder om sjön Smälten, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574002</v>
+        <v>573966</v>
       </c>
       <c r="R3" t="n">
-        <v>6347542</v>
+        <v>6347576</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,6 +866,200 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>110423641</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Utmed riksväg 37/47 söder om sjön Smälten, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>573944</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6347578</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110423643</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Utmed riksväg 37/47 söder om sjön Smälten, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>573937</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6347578</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 635-2022 artfynd.xlsx
+++ b/artfynd/A 635-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112090027</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110423640</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110423641</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110423643</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>